--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>##var</t>
   </si>
@@ -77,13 +71,55 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>DUIGroup</t>
+  </si>
+  <si>
+    <t>Bottom_1</t>
+  </si>
+  <si>
+    <t>最底层</t>
+  </si>
+  <si>
+    <t>Bottom_2</t>
+  </si>
+  <si>
+    <t>Bottom_3</t>
+  </si>
+  <si>
+    <t>Middle_1</t>
+  </si>
+  <si>
+    <t>Middle_2</t>
+  </si>
+  <si>
+    <t>Middle_3</t>
+  </si>
+  <si>
+    <t>Top_1</t>
+  </si>
+  <si>
+    <t>Top_2</t>
+  </si>
+  <si>
+    <t>Top_3</t>
+  </si>
+  <si>
+    <t>最高层</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,13 +128,151 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,12 +281,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79995117038483843"/>
+        <fgColor theme="9" tint="0.799951170384838"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -135,9 +495,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -155,17 +757,61 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -423,14 +1069,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
@@ -443,7 +1089,7 @@
     <col min="11" max="11" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +1119,7 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +1145,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="99" customHeight="1" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -529,12 +1175,99 @@
       </c>
       <c r="L3" s="1"/>
     </row>
+    <row r="4" spans="2:11">
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="8:10">
+      <c r="H5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="8:10">
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="8:10">
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="8:10">
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="8:10">
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="8:10">
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="8:10">
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="8:11">
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12">
+        <v>9</v>
+      </c>
+      <c r="K12" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -76,34 +76,34 @@
     <t>DUIGroup</t>
   </si>
   <si>
-    <t>Bottom_1</t>
+    <t>Bottom1</t>
   </si>
   <si>
     <t>最底层</t>
   </si>
   <si>
-    <t>Bottom_2</t>
-  </si>
-  <si>
-    <t>Bottom_3</t>
-  </si>
-  <si>
-    <t>Middle_1</t>
-  </si>
-  <si>
-    <t>Middle_2</t>
-  </si>
-  <si>
-    <t>Middle_3</t>
-  </si>
-  <si>
-    <t>Top_1</t>
-  </si>
-  <si>
-    <t>Top_2</t>
-  </si>
-  <si>
-    <t>Top_3</t>
+    <t>Bottom2</t>
+  </si>
+  <si>
+    <t>Bottom3</t>
+  </si>
+  <si>
+    <t>Middle1</t>
+  </si>
+  <si>
+    <t>Middle2</t>
+  </si>
+  <si>
+    <t>Middle3</t>
+  </si>
+  <si>
+    <t>Top1</t>
+  </si>
+  <si>
+    <t>Top2</t>
+  </si>
+  <si>
+    <t>Top3</t>
   </si>
   <si>
     <t>最高层</t>

--- a/DataTables/Datas/__enums__.xlsx
+++ b/DataTables/Datas/__enums__.xlsx
@@ -1,280 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>DUIGroup</t>
-  </si>
-  <si>
-    <t>Bottom1</t>
-  </si>
-  <si>
-    <t>最底层</t>
-  </si>
-  <si>
-    <t>Bottom2</t>
-  </si>
-  <si>
-    <t>Bottom3</t>
-  </si>
-  <si>
-    <t>Middle1</t>
-  </si>
-  <si>
-    <t>Middle2</t>
-  </si>
-  <si>
-    <t>Middle3</t>
-  </si>
-  <si>
-    <t>Top1</t>
-  </si>
-  <si>
-    <t>Top2</t>
-  </si>
-  <si>
-    <t>Top3</t>
-  </si>
-  <si>
-    <t>最高层</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -472,7 +369,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -593,169 +490,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -809,11 +753,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1073,193 +1080,724 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col width="19" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20.875" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.125" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.375" customWidth="1" style="4" min="6" max="6"/>
+    <col width="5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="13.5" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.25" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.125" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.125" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="4">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>DUIGroup</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>Bottom1</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>最底层</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>Bottom2</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>Bottom3</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>Middle1</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="8">
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>Middle2</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>Middle3</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>Top1</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>Top2</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>Top3</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>最高层</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VSEnemyBehavior</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ChaseSuicide</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>追击自爆</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Chase</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>追击接触伤害</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>直线横穿</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>VSWeaponBehavior</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>弹道型</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Instant</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>瞬时判定型</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>持续区域型</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VSTargetStrategy</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Nearest</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>最近</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Random</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Facing</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>面朝方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>MoveDir</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>移动方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>VSAttrType</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>生命上限</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>移速</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Might</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>威力%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>冷却%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>范围%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>弹数</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ProjSpeed</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>弹速</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>持续时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Magnet</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>磁力</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Armor</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>护甲</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Regen</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>回复</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Luck</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>幸运</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VSPickupType</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D4">
+      <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4">
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Exp</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="8:10">
-      <c r="H5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>经验</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="8:10">
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>治疗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Magnet</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="8:10">
-      <c r="H7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>全屏磁铁</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Chest</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="8:10">
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12">
-        <v>9</v>
-      </c>
-      <c r="K12" t="s">
-        <v>30</v>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>宝箱</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1267,7 +1805,6 @@
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>